--- a/data/trans_dic/P70B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,9; 95,23</t>
+          <t>81,54; 94,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,52; 92,67</t>
+          <t>64,63; 92,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,41; 92,93</t>
+          <t>79,64; 92,45</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,53; 91,79</t>
+          <t>80,52; 91,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,6; 88,42</t>
+          <t>82,81; 89,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,22; 89,25</t>
+          <t>82,18; 89,52</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,86; 94,63</t>
+          <t>88,68; 94,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,13; 90,53</t>
+          <t>84,85; 90,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,89; 91,78</t>
+          <t>87,94; 91,8</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,44; 91,19</t>
+          <t>84,17; 91,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,16; 88,43</t>
+          <t>84,08; 88,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,83; 89,29</t>
+          <t>84,56; 89,37</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109518; 125800</t>
+          <t>107715; 125329</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53625; 74697</t>
+          <t>52097; 74177</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>171034; 197666</t>
+          <t>169404; 196654</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1110468; 1265692</t>
+          <t>1110374; 1256502</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>778486; 833337</t>
+          <t>780428; 839902</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1908577; 2071782</t>
+          <t>1907701; 2078205</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>398478; 424381</t>
+          <t>397687; 424365</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>373474; 397173</t>
+          <t>372260; 396218</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>779689; 814244</t>
+          <t>780194; 814401</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1654659; 1786861</t>
+          <t>1649212; 1802222</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1230310; 1292729</t>
+          <t>1229047; 1294744</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2902407; 3054915</t>
+          <t>2893132; 3057690</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P70B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,54; 94,87</t>
+          <t>83,54; 94,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,63; 92,02</t>
+          <t>80,37; 93,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,64; 92,45</t>
+          <t>84,47; 93,04</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,52; 91,12</t>
+          <t>79,67; 84,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,81; 89,12</t>
+          <t>82,05; 86,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,18; 89,52</t>
+          <t>81,48; 84,8</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,68; 94,63</t>
+          <t>88,33; 94,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,85; 90,31</t>
+          <t>84,92; 90,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,94; 91,8</t>
+          <t>87,78; 91,83</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,17; 91,97</t>
+          <t>83,39; 87,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,08; 88,57</t>
+          <t>84,02; 87,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,56; 89,37</t>
+          <t>84,2; 86,77</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>119242</t>
+          <t>147415</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67702</t>
+          <t>77946</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186944</t>
+          <t>225361</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>107715; 125329</t>
+          <t>136950; 154908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52097; 74177</t>
+          <t>71205; 82498</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169404; 196654</t>
+          <t>213305; 234949</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1169179</t>
+          <t>1043063</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>804502</t>
+          <t>793047</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1973681</t>
+          <t>1836110</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1110374; 1256502</t>
+          <t>1009540; 1073568</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>780428; 839902</t>
+          <t>773254; 812196</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1907701; 2078205</t>
+          <t>1800389; 1873686</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>413127</t>
+          <t>451020</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>385465</t>
+          <t>424144</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>798593</t>
+          <t>875164</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>397687; 424365</t>
+          <t>432254; 462569</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>372260; 396218</t>
+          <t>409076; 435628</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>780194; 814401</t>
+          <t>852416; 891785</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1701548</t>
+          <t>1641498</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1257670</t>
+          <t>1295137</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2959218</t>
+          <t>2936635</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1649212; 1802222</t>
+          <t>1601474; 1674205</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1229047; 1294744</t>
+          <t>1271052; 1319673</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2893132; 3057690</t>
+          <t>2890626; 2979065</t>
         </is>
       </c>
     </row>
